--- a/output/pdf_financials_xlsx/ALTN.xlsx
+++ b/output/pdf_financials_xlsx/ALTN.xlsx
@@ -1644,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.161945</v>
       </c>
     </row>
     <row r="93">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.003954</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.311107</v>
       </c>
     </row>
     <row r="119">
@@ -2726,7 +2726,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -3706,7 +3710,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
         <v>-0.003954</v>
       </c>

--- a/output/pdf_financials_xlsx/ALTN.xlsx
+++ b/output/pdf_financials_xlsx/ALTN.xlsx
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.12077</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.058499</v>
       </c>
     </row>
     <row r="35">
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.12077</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.058499</v>
       </c>
     </row>
     <row r="37">
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.14291</v>
+        <v>0.02214</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.163302</v>
+        <v>0.104803</v>
       </c>
     </row>
     <row r="49">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -3660,7 +3660,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="n">
         <v>-0.012</v>
       </c>

--- a/output/pdf_financials_xlsx/ALTN.xlsx
+++ b/output/pdf_financials_xlsx/ALTN.xlsx
@@ -1869,10 +1869,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.025601</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.027915</v>
       </c>
     </row>
     <row r="111">
@@ -3324,7 +3324,11 @@
           <t>Accretion 6</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>0.025601</v>
       </c>
